--- a/Trans To Vostok/Korean/Glossary.xlsx
+++ b/Trans To Vostok/Korean/Glossary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\common\Road to Vostok\mods\Trans To Vostok\Trans To Vostok\Korean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467C5017-C9EB-4DD0-A0FB-1069DB0D00C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282DC72E-2C4D-41DB-AE6C-A6385A784DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MetaData" sheetId="1" r:id="rId1"/>
@@ -1372,7 +1372,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1578,11 +1578,180 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1668,6 +1837,55 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2177,7 +2395,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr defaultRowHeight="19.2"/>
   <cols>
     <col min="1" max="1" width="10.26953125" style="2" customWidth="1"/>
@@ -3024,39 +3242,74 @@
         <v>296</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="2">
-        <v>0</v>
-      </c>
-      <c r="B25" s="21">
-        <v>0</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" s="26" t="s">
+    <row r="25" spans="1:11" s="45" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A25" s="37">
+        <v>0</v>
+      </c>
+      <c r="B25" s="38">
+        <v>0</v>
+      </c>
+      <c r="C25" s="39">
+        <v>0</v>
+      </c>
+      <c r="D25" s="39">
+        <v>0</v>
+      </c>
+      <c r="E25" s="40">
+        <v>0</v>
+      </c>
+      <c r="F25" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="40" t="s">
         <v>227</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="K25" s="44" t="s">
         <v>261</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="21">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3079,19 +3332,19 @@
         <v>216</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3114,19 +3367,19 @@
         <v>216</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>228</v>
+        <v>124</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3155,18 +3408,18 @@
         <v>124</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" s="21">
         <v>0</v>
@@ -3187,21 +3440,21 @@
         <v>72</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" s="21">
         <v>0</v>
@@ -3222,16 +3475,16 @@
         <v>72</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3260,18 +3513,18 @@
         <v>227</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" s="21">
         <v>0</v>
@@ -3295,18 +3548,18 @@
         <v>227</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" s="21">
         <v>0</v>
@@ -3330,53 +3583,53 @@
         <v>227</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="2">
-        <v>0</v>
-      </c>
-      <c r="B35" s="21">
-        <v>0</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0</v>
-      </c>
-      <c r="F35" s="26" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="45" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A35" s="37">
+        <v>0</v>
+      </c>
+      <c r="B35" s="38">
+        <v>0</v>
+      </c>
+      <c r="C35" s="39">
+        <v>0</v>
+      </c>
+      <c r="D35" s="39">
+        <v>0</v>
+      </c>
+      <c r="E35" s="40">
+        <v>0</v>
+      </c>
+      <c r="F35" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" s="40" t="s">
         <v>227</v>
       </c>
-      <c r="I35" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>220</v>
+      <c r="I35" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="J35" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="K35" s="44" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" s="21">
         <v>0</v>
@@ -3391,27 +3644,62 @@
         <v>0</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>221</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="2">
+        <v>0</v>
+      </c>
+      <c r="B37" s="21">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" s="21">
         <v>0</v>
@@ -3432,16 +3720,16 @@
         <v>238</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>112</v>
+        <v>236</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3460,63 +3748,51 @@
       <c r="E39" s="6">
         <v>0</v>
       </c>
-      <c r="F39" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="I39" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="2">
-        <v>0</v>
-      </c>
-      <c r="B40" s="21">
-        <v>0</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="J40" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="45" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A40" s="37">
+        <v>1</v>
+      </c>
+      <c r="B40" s="38">
+        <v>0</v>
+      </c>
+      <c r="C40" s="39">
+        <v>0</v>
+      </c>
+      <c r="D40" s="39">
+        <v>0</v>
+      </c>
+      <c r="E40" s="40">
+        <v>0</v>
+      </c>
+      <c r="F40" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="G40" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="H40" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="I40" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="J40" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="K40" s="44" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" s="21">
         <v>0</v>
@@ -3530,11 +3806,23 @@
       <c r="E41" s="6">
         <v>0</v>
       </c>
+      <c r="F41" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>356</v>
+      </c>
       <c r="I41" s="10" t="s">
-        <v>229</v>
+        <v>299</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>241</v>
+        <v>70</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3554,27 +3842,62 @@
         <v>0</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>239</v>
+        <v>83</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>235</v>
+        <v>84</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>244</v>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="2">
+        <v>0</v>
+      </c>
+      <c r="B43" s="21">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" s="21">
         <v>0</v>
@@ -3592,24 +3915,24 @@
         <v>257</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>355</v>
+        <v>83</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>299</v>
+        <v>30</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>159</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B45" s="21">
         <v>0</v>
@@ -3630,16 +3953,16 @@
         <v>83</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>265</v>
+        <v>83</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>256</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3665,16 +3988,16 @@
         <v>83</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>354</v>
+        <v>37</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>255</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3703,13 +4026,13 @@
         <v>83</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -3738,13 +4061,13 @@
         <v>83</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -3773,13 +4096,13 @@
         <v>83</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3802,19 +4125,16 @@
         <v>257</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>361</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3837,19 +4157,16 @@
         <v>257</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>362</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3869,22 +4186,19 @@
         <v>0</v>
       </c>
       <c r="F52" s="26" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>358</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -3904,19 +4218,19 @@
         <v>0</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="H53" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="I53" s="10" t="s">
-        <v>273</v>
+        <v>182</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>274</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3936,19 +4250,19 @@
         <v>0</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>272</v>
+        <v>16</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>272</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>270</v>
+        <v>175</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>271</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -3977,10 +4291,10 @@
         <v>272</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>276</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -4009,10 +4323,10 @@
         <v>272</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4041,10 +4355,10 @@
         <v>272</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4073,10 +4387,10 @@
         <v>272</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>281</v>
+        <v>184</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -4105,10 +4419,10 @@
         <v>272</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>178</v>
+        <v>277</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>177</v>
+        <v>278</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4137,10 +4451,10 @@
         <v>272</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>180</v>
+        <v>279</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>179</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4169,10 +4483,10 @@
         <v>272</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4192,22 +4506,22 @@
         <v>0</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="38.4">
       <c r="A63" s="2">
         <v>0</v>
       </c>
@@ -4224,19 +4538,22 @@
         <v>0</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>280</v>
+        <v>283</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -4256,19 +4573,19 @@
         <v>0</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -4294,13 +4611,13 @@
         <v>286</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>285</v>
+        <v>69</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="38.4">
@@ -4329,13 +4646,13 @@
         <v>286</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>282</v>
+        <v>130</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>283</v>
+        <v>122</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -4364,10 +4681,13 @@
         <v>286</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>68</v>
+        <v>288</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>196</v>
+        <v>289</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -4390,19 +4710,19 @@
         <v>257</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="38.4">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="2">
         <v>0</v>
       </c>
@@ -4422,19 +4742,16 @@
         <v>257</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="K69" s="8" t="s">
-        <v>287</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -4457,19 +4774,16 @@
         <v>257</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="K70" s="8" t="s">
-        <v>290</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -4495,13 +4809,13 @@
         <v>264</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -4524,16 +4838,16 @@
         <v>257</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -4556,16 +4870,16 @@
         <v>257</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>260</v>
+        <v>115</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -4588,16 +4902,16 @@
         <v>257</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -4620,16 +4934,16 @@
         <v>257</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>134</v>
+        <v>269</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>265</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>192</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -4652,16 +4966,16 @@
         <v>257</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>134</v>
+        <v>269</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>134</v>
+        <v>321</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -4681,19 +4995,22 @@
         <v>0</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>134</v>
+        <v>269</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>134</v>
+        <v>321</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>187</v>
+        <v>169</v>
+      </c>
+      <c r="K77" s="8" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -4713,19 +5030,19 @@
         <v>0</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>269</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>265</v>
+        <v>321</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -4745,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>269</v>
@@ -4754,77 +5071,80 @@
         <v>321</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="2">
-        <v>0</v>
-      </c>
-      <c r="B80" s="21">
-        <v>0</v>
-      </c>
-      <c r="C80" s="1">
-        <v>0</v>
-      </c>
-      <c r="D80" s="1">
-        <v>0</v>
-      </c>
-      <c r="E80" s="6">
-        <v>0</v>
-      </c>
-      <c r="F80" s="26" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" s="45" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A80" s="37">
+        <v>0</v>
+      </c>
+      <c r="B80" s="38">
+        <v>0</v>
+      </c>
+      <c r="C80" s="39">
+        <v>0</v>
+      </c>
+      <c r="D80" s="39">
+        <v>0</v>
+      </c>
+      <c r="E80" s="40">
+        <v>0</v>
+      </c>
+      <c r="F80" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="G80" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="H80" s="6" t="s">
+      <c r="H80" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="I80" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="J80" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K80" s="8" t="s">
-        <v>291</v>
+      <c r="I80" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="J80" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="K80" s="44" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" s="2">
-        <v>0</v>
-      </c>
-      <c r="B81" s="21">
-        <v>0</v>
-      </c>
-      <c r="C81" s="1">
-        <v>0</v>
-      </c>
-      <c r="D81" s="1">
-        <v>0</v>
-      </c>
-      <c r="E81" s="6">
-        <v>0</v>
-      </c>
-      <c r="F81" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="H81" s="6" t="s">
+      <c r="A81" s="29">
+        <v>0</v>
+      </c>
+      <c r="B81" s="30">
+        <v>0</v>
+      </c>
+      <c r="C81" s="31">
+        <v>0</v>
+      </c>
+      <c r="D81" s="31">
+        <v>0</v>
+      </c>
+      <c r="E81" s="32">
+        <v>0</v>
+      </c>
+      <c r="F81" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="G81" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="I81" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J81" s="12" t="s">
-        <v>167</v>
+      <c r="H81" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="I81" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="J81" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="K81" s="36" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -4844,19 +5164,22 @@
         <v>0</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>267</v>
+        <v>57</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -4876,22 +5199,57 @@
         <v>0</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="H83" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="K83" s="8" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="2">
+        <v>0</v>
+      </c>
+      <c r="B84" s="21">
+        <v>0</v>
+      </c>
+      <c r="C84" s="1">
+        <v>0</v>
+      </c>
+      <c r="D84" s="1">
+        <v>0</v>
+      </c>
+      <c r="E84" s="6">
+        <v>0</v>
+      </c>
+      <c r="F84" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="G84" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="I83" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="J83" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="K83" s="8" t="s">
-        <v>173</v>
+      <c r="H84" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="I84" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="J84" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="K84" s="8" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -4920,13 +5278,13 @@
         <v>357</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>56</v>
+        <v>300</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4955,13 +5313,13 @@
         <v>357</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>57</v>
+        <v>301</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -4990,13 +5348,13 @@
         <v>357</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>46</v>
+        <v>309</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -5025,13 +5383,13 @@
         <v>357</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>308</v>
+        <v>48</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>310</v>
+        <v>59</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -5060,13 +5418,13 @@
         <v>357</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>308</v>
+        <v>49</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -5095,13 +5453,13 @@
         <v>357</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>47</v>
+        <v>311</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>301</v>
+        <v>62</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -5130,13 +5488,13 @@
         <v>357</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>61</v>
+        <v>303</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -5165,13 +5523,13 @@
         <v>357</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K92" s="8" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -5200,13 +5558,13 @@
         <v>357</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -5235,13 +5593,13 @@
         <v>357</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>311</v>
+        <v>52</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K94" s="8" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -5270,13 +5628,13 @@
         <v>357</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>303</v>
+        <v>66</v>
       </c>
       <c r="K95" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -5305,13 +5663,13 @@
         <v>357</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>50</v>
+        <v>312</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -5340,13 +5698,13 @@
         <v>357</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -5375,13 +5733,13 @@
         <v>357</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>52</v>
+        <v>317</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>65</v>
+        <v>304</v>
       </c>
       <c r="K98" s="8" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -5410,13 +5768,13 @@
         <v>357</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>53</v>
+        <v>317</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>66</v>
+        <v>318</v>
       </c>
       <c r="K99" s="8" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -5445,48 +5803,48 @@
         <v>357</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>312</v>
+        <v>209</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>67</v>
+        <v>318</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
-      <c r="A101" s="2">
-        <v>0</v>
-      </c>
-      <c r="B101" s="21">
-        <v>0</v>
-      </c>
-      <c r="C101" s="1">
-        <v>0</v>
-      </c>
-      <c r="D101" s="1">
-        <v>0</v>
-      </c>
-      <c r="E101" s="6">
-        <v>0</v>
-      </c>
-      <c r="F101" s="26" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" s="45" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A101" s="37">
+        <v>0</v>
+      </c>
+      <c r="B101" s="38">
+        <v>0</v>
+      </c>
+      <c r="C101" s="39">
+        <v>0</v>
+      </c>
+      <c r="D101" s="39">
+        <v>0</v>
+      </c>
+      <c r="E101" s="40">
+        <v>0</v>
+      </c>
+      <c r="F101" s="41" t="s">
         <v>264</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="G101" s="39" t="s">
         <v>321</v>
       </c>
-      <c r="H101" s="6" t="s">
+      <c r="H101" s="40" t="s">
         <v>357</v>
       </c>
-      <c r="I101" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="J101" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K101" s="8" t="s">
-        <v>335</v>
+      <c r="I101" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="J101" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="K101" s="44" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -5506,22 +5864,22 @@
         <v>0</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>321</v>
+        <v>246</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>357</v>
+        <v>248</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>317</v>
+        <v>232</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>304</v>
+        <v>233</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -5541,22 +5899,22 @@
         <v>0</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>321</v>
+        <v>246</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>357</v>
+        <v>247</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>317</v>
+        <v>110</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>318</v>
+        <v>157</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>319</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -5576,22 +5934,19 @@
         <v>0</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>209</v>
+        <v>336</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="K104" s="8" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -5611,22 +5966,51 @@
         <v>0</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="K105" s="8" t="s">
-        <v>315</v>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="2">
+        <v>0</v>
+      </c>
+      <c r="B106" s="21">
+        <v>0</v>
+      </c>
+      <c r="C106" s="1">
+        <v>0</v>
+      </c>
+      <c r="D106" s="1">
+        <v>0</v>
+      </c>
+      <c r="E106" s="6">
+        <v>0</v>
+      </c>
+      <c r="F106" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="I106" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="J106" s="12" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -5646,22 +6030,19 @@
         <v>0</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>134</v>
+        <v>340</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>246</v>
+        <v>341</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>248</v>
+        <v>351</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>232</v>
+        <v>339</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="K107" s="8" t="s">
-        <v>250</v>
+        <v>346</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -5681,22 +6062,51 @@
         <v>0</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>134</v>
+        <v>340</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>246</v>
+        <v>350</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>247</v>
+        <v>351</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>110</v>
+        <v>342</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="K108" s="8" t="s">
-        <v>249</v>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="2">
+        <v>0</v>
+      </c>
+      <c r="B109" s="21">
+        <v>0</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0</v>
+      </c>
+      <c r="D109" s="1">
+        <v>0</v>
+      </c>
+      <c r="E109" s="6">
+        <v>0</v>
+      </c>
+      <c r="F109" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="I109" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="J109" s="12" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -5719,16 +6129,16 @@
         <v>340</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>341</v>
+        <v>134</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>351</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -5748,244 +6158,66 @@
         <v>0</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>337</v>
+        <v>17</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
-      <c r="A112" s="2">
-        <v>0</v>
-      </c>
-      <c r="B112" s="21">
-        <v>0</v>
-      </c>
-      <c r="C112" s="1">
-        <v>0</v>
-      </c>
-      <c r="D112" s="1">
-        <v>0</v>
-      </c>
-      <c r="E112" s="6">
-        <v>0</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="I112" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="J112" s="12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" s="2">
-        <v>0</v>
-      </c>
-      <c r="B113" s="21">
-        <v>0</v>
-      </c>
-      <c r="C113" s="1">
-        <v>0</v>
-      </c>
-      <c r="D113" s="1">
-        <v>0</v>
-      </c>
-      <c r="E113" s="6">
-        <v>0</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="H113" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="I113" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="J113" s="12" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" s="2">
-        <v>0</v>
-      </c>
-      <c r="B114" s="21">
-        <v>0</v>
-      </c>
-      <c r="C114" s="1">
-        <v>0</v>
-      </c>
-      <c r="D114" s="1">
-        <v>0</v>
-      </c>
-      <c r="E114" s="6">
-        <v>0</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="I114" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="J114" s="12" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115" s="2">
-        <v>0</v>
-      </c>
-      <c r="B115" s="21">
-        <v>0</v>
-      </c>
-      <c r="C115" s="1">
-        <v>0</v>
-      </c>
-      <c r="D115" s="1">
-        <v>0</v>
-      </c>
-      <c r="E115" s="6">
-        <v>0</v>
-      </c>
-      <c r="F115" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="I115" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="J115" s="12" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
-      <c r="A116" s="2">
-        <v>0</v>
-      </c>
-      <c r="B116" s="21">
-        <v>0</v>
-      </c>
-      <c r="C116" s="1">
-        <v>0</v>
-      </c>
-      <c r="D116" s="1">
-        <v>0</v>
-      </c>
-      <c r="E116" s="6">
-        <v>0</v>
-      </c>
-      <c r="F116" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="I116" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="J116" s="12" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
-      <c r="A118" s="2">
-        <v>0</v>
-      </c>
-      <c r="B118" s="21">
-        <v>0</v>
-      </c>
-      <c r="C118" s="1">
-        <v>0</v>
-      </c>
-      <c r="D118" s="1">
-        <v>0</v>
-      </c>
-      <c r="E118" s="6">
-        <v>0</v>
-      </c>
-      <c r="F118" s="26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" s="45" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A112" s="37">
+        <v>0</v>
+      </c>
+      <c r="B112" s="38">
+        <v>0</v>
+      </c>
+      <c r="C112" s="39">
+        <v>0</v>
+      </c>
+      <c r="D112" s="39">
+        <v>0</v>
+      </c>
+      <c r="E112" s="40">
+        <v>0</v>
+      </c>
+      <c r="F112" s="41" t="s">
         <v>364</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="G112" s="39" t="s">
         <v>355</v>
       </c>
-      <c r="H118" s="6" t="s">
+      <c r="H112" s="40" t="s">
         <v>365</v>
       </c>
-      <c r="I118" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J118" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
-      <c r="A119" s="2">
-        <v>0</v>
-      </c>
-      <c r="B119" s="21">
-        <v>0</v>
-      </c>
-      <c r="C119" s="1">
-        <v>0</v>
-      </c>
-      <c r="D119" s="1">
-        <v>0</v>
-      </c>
-      <c r="E119" s="6">
-        <v>0</v>
-      </c>
-      <c r="F119" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="H119" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="I119" s="10" t="s">
+      <c r="I112" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="J119" s="12" t="s">
+      <c r="J112" s="43" t="s">
         <v>12</v>
       </c>
+      <c r="K112" s="44"/>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" s="29"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="31"/>
+      <c r="D113" s="31"/>
+      <c r="E113" s="32"/>
+      <c r="F113" s="33"/>
+      <c r="G113" s="31"/>
+      <c r="H113" s="32"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
+      <c r="K113" s="36"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
